--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NORTH_CAROLINA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NORTH_CAROLINA_2013.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C136">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C187">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C316">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C758">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C908">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C909">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C971">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C972">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C979">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1162">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1448">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1606">
